--- a/data/trans_dic/P19C08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,08</t>
+          <t>0,23; 2,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,03</t>
+          <t>0,48; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,54</t>
+          <t>0,09; 1,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,27</t>
+          <t>0,14; 1,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,3</t>
+          <t>0,15; 1,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,24</t>
+          <t>0,29; 2,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,05</t>
+          <t>0,19; 1,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,07</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,54; 3,27</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,85</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,27</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 3,2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,61</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,68</t>
+          <t>0,12; 1,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,09</t>
+          <t>0,44; 2,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,16; 1,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,93</t>
+          <t>0,13; 0,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,59</t>
+          <t>0,11; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,34</t>
+          <t>0,09; 1,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,88</t>
+          <t>0,11; 0,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,02; 0,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,56</t>
+          <t>0,28; 1,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,25</t>
+          <t>0,14; 1,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,79</t>
+          <t>0,13; 0,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,89</t>
+          <t>0,23; 0,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,64</t>
+          <t>0,12; 0,67</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,61</t>
+          <t>0,47; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,48</t>
+          <t>0,2; 2,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,7</t>
+          <t>0,14; 1,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,43</t>
+          <t>0,13; 1,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,73</t>
+          <t>0,36; 1,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,67</t>
+          <t>0,08; 1,45</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,96</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,37</t>
+          <t>0,23; 1,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,18</t>
+          <t>0,17; 1,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,0</t>
+          <t>0,1; 0,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,22</t>
+          <t>0,27; 1,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,81</t>
+          <t>0,13; 0,85</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,61</t>
+          <t>0,19; 0,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,97</t>
+          <t>0,33; 1,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,81</t>
+          <t>0,22; 0,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,92</t>
+          <t>0,3; 0,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,93</t>
+          <t>0,38; 0,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,46</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,61</t>
+          <t>0,23; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,66</t>
+          <t>0,29; 0,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,88</t>
+          <t>0,41; 0,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,34</t>
+          <t>0,09; 0,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,61</t>
+          <t>0,27; 0,6</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>876; 8026</t>
+          <t>880; 8254</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1842; 15942</t>
+          <t>1912; 17145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4905</t>
+          <t>0; 5133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>478; 7686</t>
+          <t>466; 7254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 6074</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5778</t>
+          <t>0; 4887</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>601; 5587</t>
+          <t>607; 5151</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1008; 8481</t>
+          <t>955; 8634</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1967; 15468</t>
+          <t>1999; 15640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5223</t>
+          <t>0; 5176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1816; 9819</t>
+          <t>1773; 9704</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5575</t>
+          <t>0; 6438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6785</t>
+          <t>0; 7573</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1875; 10675</t>
+          <t>1817; 10909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6762</t>
+          <t>0; 5790</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5355</t>
+          <t>0; 4249</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>443; 6338</t>
+          <t>442; 6137</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2879; 13231</t>
+          <t>2776; 13334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>965; 9218</t>
+          <t>1096; 9045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 5238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1008; 7669</t>
+          <t>1052; 7510</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8123</t>
+          <t>0; 10045</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6494</t>
+          <t>0; 5780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638; 10486</t>
+          <t>740; 10960</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6054</t>
+          <t>0; 5222</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8067</t>
+          <t>0; 7227</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3105</t>
+          <t>0; 3480</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 12239</t>
+          <t>0; 10191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 10182</t>
+          <t>0; 9488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1134; 11040</t>
+          <t>759; 10423</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>929; 7642</t>
+          <t>929; 8545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>813; 7631</t>
+          <t>812; 7747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 7396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>161; 5416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7059</t>
+          <t>0; 6188</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1907; 10913</t>
+          <t>1927; 10724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6722</t>
+          <t>0; 6278</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1486; 12025</t>
+          <t>1370; 11225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1883; 11572</t>
+          <t>1886; 10681</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3880; 14954</t>
+          <t>3775; 14527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 7561</t>
+          <t>0; 8321</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2383; 12494</t>
+          <t>2318; 13164</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1887; 10540</t>
+          <t>1888; 10598</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 19185</t>
+          <t>0; 18258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>938; 11306</t>
+          <t>930; 10585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>953; 11342</t>
+          <t>947; 10563</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7052</t>
+          <t>0; 7922</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>0; 3753</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>929; 10058</t>
+          <t>934; 10367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4024; 18555</t>
+          <t>3875; 17505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>917; 8168</t>
+          <t>913; 8081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>740; 20975</t>
+          <t>1032; 18193</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5754</t>
+          <t>0; 5270</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4751</t>
+          <t>0; 5110</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>909; 9104</t>
+          <t>907; 8787</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2989; 12624</t>
+          <t>2143; 13204</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1396; 8741</t>
+          <t>1240; 8284</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>965; 11525</t>
+          <t>1182; 10293</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3077; 13963</t>
+          <t>3124; 15548</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2051</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1116; 7867</t>
+          <t>1242; 8279</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3771; 14987</t>
+          <t>4545; 15799</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9975; 28374</t>
+          <t>9613; 29013</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1038; 10314</t>
+          <t>1148; 10311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7059; 26611</t>
+          <t>7283; 27432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8295; 25233</t>
+          <t>8210; 23476</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11288; 29267</t>
+          <t>11911; 29598</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1937; 13200</t>
+          <t>2175; 14009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8237; 21182</t>
+          <t>8184; 21309</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14774; 34413</t>
+          <t>14862; 34778</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26186; 52977</t>
+          <t>24967; 51781</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4723; 18904</t>
+          <t>4902; 19237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18901; 41402</t>
+          <t>18116; 40449</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,14</t>
+          <t>0,22; 1,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,34</t>
+          <t>0,49; 3,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,46</t>
+          <t>0,09; 1,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,17</t>
+          <t>0,14; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,32</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,27</t>
+          <t>0,28; 2,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,03</t>
+          <t>0,23; 1,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,85</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,53; 3,24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,97</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,07</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 3,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,85</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,63</t>
+          <t>0,11; 1,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,1</t>
+          <t>0,43; 2,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,3</t>
+          <t>0,14; 1,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,91</t>
+          <t>0,12; 0,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,66</t>
+          <t>0,35; 2,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,19 +1022,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,03</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,9</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,17</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,18</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,11</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,26</t>
+          <t>0,3; 1,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,98</t>
+          <t>0,11; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,54</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,53</t>
+          <t>0,27; 1,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,17</t>
+          <t>0,23; 1,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,87</t>
+          <t>0,22; 0,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,67</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,63</t>
+          <t>0,47; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,32</t>
+          <t>0,2; 2,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,58</t>
+          <t>0,14; 1,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,47</t>
+          <t>0,13; 1,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,63</t>
+          <t>0,36; 1,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,82</t>
+          <t>0,09; 0,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,45</t>
+          <t>0,11; 1,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,1; 0,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,43</t>
+          <t>0,24; 1,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,11</t>
+          <t>0,23; 1,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,08; 0,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,36</t>
+          <t>0,27; 1,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,85</t>
+          <t>0,17; 0,96</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,65</t>
+          <t>0,15; 0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,0</t>
+          <t>0,36; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,39</t>
+          <t>0,04; 0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,84</t>
+          <t>0,28; 0,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,86</t>
+          <t>0,3; 0,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,94</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,07; 0,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,61</t>
+          <t>0,29; 0,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,67</t>
+          <t>0,28; 0,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,86</t>
+          <t>0,4; 0,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,6</t>
+          <t>0,33; 0,71</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>5401</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>880; 8254</t>
+          <t>867; 7428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1912; 17145</t>
+          <t>1943; 14789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5133</t>
+          <t>0; 5930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>466; 7254</t>
+          <t>506; 7456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6074</t>
+          <t>0; 5691</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 4862</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>607; 5151</t>
+          <t>683; 6682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>955; 8634</t>
+          <t>979; 9604</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1999; 15640</t>
+          <t>1964; 17083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5176</t>
+          <t>0; 4821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1773; 9704</t>
+          <t>2304; 11117</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3564</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6438</t>
+          <t>0; 5550</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7573</t>
+          <t>0; 7094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1817; 10909</t>
+          <t>1778; 10815</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5790</t>
+          <t>0; 6188</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>442; 6137</t>
+          <t>459; 6932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2776; 13334</t>
+          <t>2745; 13202</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1096; 9045</t>
+          <t>947; 9737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5238</t>
+          <t>0; 5241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1052; 7510</t>
+          <t>1044; 8165</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>658</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5052</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10045</t>
+          <t>0; 9536</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5780</t>
+          <t>0; 5502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>740; 10960</t>
+          <t>1605; 9589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5222</t>
+          <t>0; 7294</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7227</t>
+          <t>0; 6836</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3480</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 10191</t>
+          <t>0; 10913</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 9488</t>
+          <t>0; 8953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>759; 10423</t>
+          <t>1922; 10844</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>8376</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>929; 8545</t>
+          <t>935; 9133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>812; 7747</t>
+          <t>814; 7895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7396</t>
+          <t>0; 5105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>161; 5416</t>
+          <t>0; 13649</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6188</t>
+          <t>0; 7025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1927; 10724</t>
+          <t>1913; 10639</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6278</t>
+          <t>0; 5795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1370; 11225</t>
+          <t>1918; 12745</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1886; 10681</t>
+          <t>1943; 10744</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3775; 14527</t>
+          <t>3730; 15230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8321</t>
+          <t>0; 7733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2318; 13164</t>
+          <t>3333; 18962</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5751</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1888; 10598</t>
+          <t>1906; 10739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 18258</t>
+          <t>0; 15328</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>930; 10585</t>
+          <t>933; 11224</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>947; 10563</t>
+          <t>952; 11528</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7922</t>
+          <t>0; 7646</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 4932</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>934; 10367</t>
+          <t>936; 11655</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3875; 17505</t>
+          <t>3892; 17170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>913; 8081</t>
+          <t>912; 9235</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1032; 18193</t>
+          <t>1399; 19725</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4623</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5270</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5110</t>
+          <t>0; 4481</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>907; 8787</t>
+          <t>910; 8864</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2143; 13204</t>
+          <t>2249; 13082</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1240; 8284</t>
+          <t>1860; 10499</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1182; 10293</t>
+          <t>971; 10268</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3124; 15548</t>
+          <t>3148; 13795</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1242; 8279</t>
+          <t>1736; 10028</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27181</t>
+          <t>32766</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4545; 15799</t>
+          <t>3735; 15022</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9613; 29013</t>
+          <t>10545; 30885</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1148; 10311</t>
+          <t>1147; 11082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7283; 27432</t>
+          <t>9306; 32034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8210; 23476</t>
+          <t>8102; 23314</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11911; 29598</t>
+          <t>11668; 29468</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2175; 14009</t>
+          <t>1964; 13394</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8184; 21309</t>
+          <t>10328; 24868</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14862; 34778</t>
+          <t>14626; 34922</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24967; 51781</t>
+          <t>24506; 53483</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4902; 19237</t>
+          <t>5157; 19095</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18116; 40449</t>
+          <t>22268; 48513</t>
         </is>
       </c>
     </row>
